--- a/ocorrencias.xlsx
+++ b/ocorrencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anac-my.sharepoint.com/personal/luiz_beltrao_anac_gov_br/Documents/7 - CGDIN/SEI/Verificação semanal LGPD/Painel de controle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="8_{B08CBB39-7D29-48D2-BF0D-F3F98B4AE0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9B72770-B707-4C39-A25C-B65B3F3ECE7A}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="8_{B08CBB39-7D29-48D2-BF0D-F3F98B4AE0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{522B82A2-DD48-40B6-B254-B7EBC5B26529}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="8" activeTab="12" xr2:uid="{A9AF6F09-8019-4632-99BD-44582E7A76AD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="9" activeTab="13" xr2:uid="{A9AF6F09-8019-4632-99BD-44582E7A76AD}"/>
   </bookViews>
   <sheets>
     <sheet name="1 a 8.06" sheetId="2" r:id="rId1"/>
@@ -26,6 +26,7 @@
     <sheet name="12_ a 18_08" sheetId="11" r:id="rId11"/>
     <sheet name="19 a 25_8" sheetId="12" r:id="rId12"/>
     <sheet name="26 a 01_09" sheetId="13" r:id="rId13"/>
+    <sheet name="02 a 08_09" sheetId="14" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'07 a 13.07'!$A$4:$B$4</definedName>
@@ -56,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="176">
   <si>
     <t>Código</t>
   </si>
@@ -578,6 +579,12 @@
   </si>
   <si>
     <t>SAG</t>
+  </si>
+  <si>
+    <t>CCIM</t>
+  </si>
+  <si>
+    <t>COAG-BHZ</t>
   </si>
 </sst>
 </file>
@@ -3674,6 +3681,590 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2E7ADC-9C1C-4EA2-98B2-C12ABC97B3B2}">
+  <dimension ref="A2:C56"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.7265625" customWidth="1"/>
+    <col min="2" max="2" width="16.36328125" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="B2" s="11">
+        <f>C56</f>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="8">
+        <v>42</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="8">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="8">
+        <v>32</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" s="8">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="8">
+        <v>31</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C7" s="8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="8">
+        <v>36</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C8" s="8">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="8">
+        <v>30</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C9" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="8">
+        <v>41</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="8">
+        <v>34</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="8">
+        <v>1</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="8">
+        <v>26</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="8">
+        <v>2</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="8">
+        <v>11</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="8">
+        <v>3</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="C16" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="8">
+        <v>9</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="8">
+        <v>7</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C18" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="8">
+        <v>5</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C19" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="8">
+        <v>4</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C20" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="8">
+        <v>22</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="8">
+        <v>17</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="C22" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="8">
+        <v>38</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="8">
+        <v>8</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C24" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="8">
+        <v>40</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="8">
+        <v>23</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="C26" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="8">
+        <v>21</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C27" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="8">
+        <v>33</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C28" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="8">
+        <v>46</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="8">
+        <v>44</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="8">
+        <v>16</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C31" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" s="8">
+        <v>13</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="8">
+        <v>10</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C33" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" s="8">
+        <v>6</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="C34" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="8">
+        <v>0</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C35" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="8">
+        <v>12</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="C36" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" s="8">
+        <v>15</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="C37" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" s="8">
+        <v>14</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" s="8">
+        <v>25</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" s="8">
+        <v>27</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C40" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" s="8">
+        <v>24</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C41" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" s="8">
+        <v>18</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C42" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" s="8">
+        <v>19</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" s="8">
+        <v>20</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C44" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" s="8">
+        <v>28</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C45" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" s="8">
+        <v>29</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="C46" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" s="8">
+        <v>35</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C47" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" s="8">
+        <v>37</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C48" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" s="8">
+        <v>39</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C49" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" s="8">
+        <v>43</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" s="8">
+        <v>45</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C51" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" s="8">
+        <v>47</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C52" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" s="8"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" s="8"/>
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C56" s="13">
+        <f>SUM(C5:C55)</f>
+        <v>185</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31DC5A72-105B-4A74-9A40-6DECF5B03B2D}">
   <dimension ref="A2:B61"/>
@@ -7447,6 +8038,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B2C160DC8B30F54783CACC61231B8252" ma:contentTypeVersion="14" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="1f908957678d77794d61d7fffe93fc41">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="583a6060-d1b7-45db-b4d6-660de356d713" xmlns:ns3="97cc50e0-5e48-4896-9dff-357abd4c15c7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0aa59e2dacabcbe879c9d2919b50461b" ns2:_="" ns3:_="">
     <xsd:import namespace="583a6060-d1b7-45db-b4d6-660de356d713"/>
@@ -7675,15 +8275,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD91E5EA-D116-4795-B575-F86A672AE76F}">
   <ds:schemaRefs>
@@ -7702,6 +8293,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BDE4EE3-4557-4002-B14D-2B12156DBD9E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{907A6689-E3B8-4B0E-A078-95B4FF1401C0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7718,12 +8317,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BDE4EE3-4557-4002-B14D-2B12156DBD9E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/ocorrencias.xlsx
+++ b/ocorrencias.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anac-my.sharepoint.com/personal/luiz_beltrao_anac_gov_br/Documents/7 - CGDIN/SEI/Verificação semanal LGPD/Painel de controle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="8_{B08CBB39-7D29-48D2-BF0D-F3F98B4AE0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{522B82A2-DD48-40B6-B254-B7EBC5B26529}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="8_{B08CBB39-7D29-48D2-BF0D-F3F98B4AE0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{580A2D64-FE55-46C5-9F16-409D7C8553A8}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="9" activeTab="13" xr2:uid="{A9AF6F09-8019-4632-99BD-44582E7A76AD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="10" activeTab="14" xr2:uid="{A9AF6F09-8019-4632-99BD-44582E7A76AD}"/>
   </bookViews>
   <sheets>
     <sheet name="1 a 8.06" sheetId="2" r:id="rId1"/>
@@ -27,6 +27,7 @@
     <sheet name="19 a 25_8" sheetId="12" r:id="rId12"/>
     <sheet name="26 a 01_09" sheetId="13" r:id="rId13"/>
     <sheet name="02 a 08_09" sheetId="14" r:id="rId14"/>
+    <sheet name="09 a 15_09" sheetId="15" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'07 a 13.07'!$A$4:$B$4</definedName>
@@ -57,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="181">
   <si>
     <t>Código</t>
   </si>
@@ -585,6 +586,21 @@
   </si>
   <si>
     <t>COAG-BHZ</t>
+  </si>
+  <si>
+    <t>CGRA</t>
+  </si>
+  <si>
+    <t>ACP-SAR</t>
+  </si>
+  <si>
+    <t>COJOR</t>
+  </si>
+  <si>
+    <t>RPS-GAPE</t>
+  </si>
+  <si>
+    <t>SPO</t>
   </si>
 </sst>
 </file>
@@ -712,10 +728,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4265,6 +4277,602 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AE61881-7358-4508-9676-7471149863B7}">
+  <dimension ref="A2:C56"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.7265625" customWidth="1"/>
+    <col min="2" max="2" width="16.36328125" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="B2" s="11">
+        <f>C56</f>
+        <v>235</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="8">
+        <v>40</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="8">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="8">
+        <v>33</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" s="8">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="8">
+        <v>34</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7" s="8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="8">
+        <v>11</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="8">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="8">
+        <v>7</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C9" s="8">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="8">
+        <v>3</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="8">
+        <v>39</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="8">
+        <v>6</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C12" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="8">
+        <v>13</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="8">
+        <v>35</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="8">
+        <v>9</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C15" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="8">
+        <v>2</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="8">
+        <v>45</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="8">
+        <v>16</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="8">
+        <v>18</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C19" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="8">
+        <v>26</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="C20" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="8">
+        <v>47</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="8">
+        <v>36</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C22" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="8">
+        <v>1</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C23" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="8">
+        <v>14</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="C24" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="8">
+        <v>25</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="8">
+        <v>21</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="8">
+        <v>22</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="8">
+        <v>4</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="8">
+        <v>12</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C29" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="8">
+        <v>8</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="C30" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="8">
+        <v>49</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" s="8">
+        <v>42</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C32" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="8">
+        <v>43</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" s="8">
+        <v>15</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="8">
+        <v>5</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="C35" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="8">
+        <v>27</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C36" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" s="8">
+        <v>19</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="C37" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" s="8">
+        <v>32</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C38" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" s="8">
+        <v>37</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C39" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" s="8">
+        <v>17</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C40" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" s="8">
+        <v>0</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C41" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" s="8">
+        <v>10</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C42" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" s="8">
+        <v>23</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="C43" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" s="8">
+        <v>20</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C44" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" s="8">
+        <v>24</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C45" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" s="8">
+        <v>29</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C46" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" s="8">
+        <v>30</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C47" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" s="8">
+        <v>31</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C48" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" s="8">
+        <v>28</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" s="8">
+        <v>38</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C50" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" s="8">
+        <v>41</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="C51" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" s="8">
+        <v>44</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C52" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" s="8">
+        <v>46</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="C53" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" s="8">
+        <v>48</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="C54" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C56" s="6">
+        <f>SUM(C5:C55)</f>
+        <v>235</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31DC5A72-105B-4A74-9A40-6DECF5B03B2D}">
   <dimension ref="A2:B61"/>
@@ -8027,26 +8635,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="583a6060-d1b7-45db-b4d6-660de356d713">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="97cc50e0-5e48-4896-9dff-357abd4c15c7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B2C160DC8B30F54783CACC61231B8252" ma:contentTypeVersion="14" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="1f908957678d77794d61d7fffe93fc41">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="583a6060-d1b7-45db-b4d6-660de356d713" xmlns:ns3="97cc50e0-5e48-4896-9dff-357abd4c15c7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0aa59e2dacabcbe879c9d2919b50461b" ns2:_="" ns3:_="">
     <xsd:import namespace="583a6060-d1b7-45db-b4d6-660de356d713"/>
@@ -8275,32 +8863,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD91E5EA-D116-4795-B575-F86A672AE76F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="583a6060-d1b7-45db-b4d6-660de356d713"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="97cc50e0-5e48-4896-9dff-357abd4c15c7"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BDE4EE3-4557-4002-B14D-2B12156DBD9E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="583a6060-d1b7-45db-b4d6-660de356d713">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="97cc50e0-5e48-4896-9dff-357abd4c15c7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{907A6689-E3B8-4B0E-A078-95B4FF1401C0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8317,4 +8900,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BDE4EE3-4557-4002-B14D-2B12156DBD9E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD91E5EA-D116-4795-B575-F86A672AE76F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="583a6060-d1b7-45db-b4d6-660de356d713"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="97cc50e0-5e48-4896-9dff-357abd4c15c7"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/ocorrencias.xlsx
+++ b/ocorrencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anac-my.sharepoint.com/personal/luiz_beltrao_anac_gov_br/Documents/7 - CGDIN/SEI/Verificação semanal LGPD/Painel de controle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="55" documentId="8_{B08CBB39-7D29-48D2-BF0D-F3F98B4AE0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{580A2D64-FE55-46C5-9F16-409D7C8553A8}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="8_{B08CBB39-7D29-48D2-BF0D-F3F98B4AE0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22F0DDF6-78DE-4FA0-A05E-AFEA7909C12D}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="10" activeTab="14" xr2:uid="{A9AF6F09-8019-4632-99BD-44582E7A76AD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="10" activeTab="15" xr2:uid="{A9AF6F09-8019-4632-99BD-44582E7A76AD}"/>
   </bookViews>
   <sheets>
     <sheet name="1 a 8.06" sheetId="2" r:id="rId1"/>
@@ -28,6 +28,7 @@
     <sheet name="26 a 01_09" sheetId="13" r:id="rId13"/>
     <sheet name="02 a 08_09" sheetId="14" r:id="rId14"/>
     <sheet name="09 a 15_09" sheetId="15" r:id="rId15"/>
+    <sheet name="16 a 22_09" sheetId="16" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'07 a 13.07'!$A$4:$B$4</definedName>
@@ -58,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="184">
   <si>
     <t>Código</t>
   </si>
@@ -601,6 +602,15 @@
   </si>
   <si>
     <t>SPO</t>
+  </si>
+  <si>
+    <t>SGP</t>
+  </si>
+  <si>
+    <t>GDPE</t>
+  </si>
+  <si>
+    <t>GTVC-145</t>
   </si>
 </sst>
 </file>
@@ -4873,6 +4883,590 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B679332-A8A6-4022-86D6-C760D1EF25E5}">
+  <dimension ref="A2:C56"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.7265625" customWidth="1"/>
+    <col min="2" max="2" width="16.36328125" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="B2" s="11">
+        <f>C56</f>
+        <v>233</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="8">
+        <v>38</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="8">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="8">
+        <v>27</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" s="8">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="8">
+        <v>28</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7" s="8">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="8">
+        <v>0</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="8">
+        <v>4</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C9" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="8">
+        <v>26</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C10" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="8">
+        <v>47</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="8">
+        <v>40</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C12" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="8">
+        <v>19</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="C13" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="8">
+        <v>23</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="8">
+        <v>1</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="8">
+        <v>9</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="8">
+        <v>10</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="8">
+        <v>14</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C18" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="8">
+        <v>37</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="8">
+        <v>32</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C20" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="8">
+        <v>44</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="C21" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="8">
+        <v>13</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="8">
+        <v>5</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="C23" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="8">
+        <v>43</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="8">
+        <v>30</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="8">
+        <v>25</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="8">
+        <v>7</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C27" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="8">
+        <v>12</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="8">
+        <v>45</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="C29" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="8">
+        <v>36</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="8">
+        <v>35</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" s="8">
+        <v>33</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C32" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="8">
+        <v>6</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C33" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" s="8">
+        <v>2</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="C34" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="8">
+        <v>16</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C35" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="8">
+        <v>18</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C36" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" s="8">
+        <v>21</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" s="8">
+        <v>11</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="C38" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" s="8">
+        <v>8</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C39" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" s="8">
+        <v>3</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C40" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" s="8">
+        <v>15</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="C41" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" s="8">
+        <v>17</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C42" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" s="8">
+        <v>20</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C43" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" s="8">
+        <v>22</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C44" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" s="8">
+        <v>31</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C45" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" s="8">
+        <v>29</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C46" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" s="8">
+        <v>24</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="C47" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" s="8">
+        <v>34</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C48" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" s="8">
+        <v>39</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C49" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" s="8">
+        <v>41</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="C50" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" s="8">
+        <v>42</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" s="8">
+        <v>46</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C52" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" s="8"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" s="8"/>
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C56" s="6">
+        <f>SUM(C5:C55)</f>
+        <v>233</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31DC5A72-105B-4A74-9A40-6DECF5B03B2D}">
   <dimension ref="A2:B61"/>
@@ -8635,6 +9229,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B2C160DC8B30F54783CACC61231B8252" ma:contentTypeVersion="14" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="1f908957678d77794d61d7fffe93fc41">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="583a6060-d1b7-45db-b4d6-660de356d713" xmlns:ns3="97cc50e0-5e48-4896-9dff-357abd4c15c7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0aa59e2dacabcbe879c9d2919b50461b" ns2:_="" ns3:_="">
     <xsd:import namespace="583a6060-d1b7-45db-b4d6-660de356d713"/>
@@ -8863,15 +9466,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -8884,6 +9478,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BDE4EE3-4557-4002-B14D-2B12156DBD9E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{907A6689-E3B8-4B0E-A078-95B4FF1401C0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8898,14 +9500,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BDE4EE3-4557-4002-B14D-2B12156DBD9E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/ocorrencias.xlsx
+++ b/ocorrencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anac-my.sharepoint.com/personal/luiz_beltrao_anac_gov_br/Documents/7 - CGDIN/SEI/Verificação semanal LGPD/Painel de controle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="8_{B08CBB39-7D29-48D2-BF0D-F3F98B4AE0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22F0DDF6-78DE-4FA0-A05E-AFEA7909C12D}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="8_{B08CBB39-7D29-48D2-BF0D-F3F98B4AE0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8A8932E-DDD4-4018-8945-96876C33AA53}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="10" activeTab="15" xr2:uid="{A9AF6F09-8019-4632-99BD-44582E7A76AD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="11" activeTab="16" xr2:uid="{A9AF6F09-8019-4632-99BD-44582E7A76AD}"/>
   </bookViews>
   <sheets>
     <sheet name="1 a 8.06" sheetId="2" r:id="rId1"/>
@@ -29,6 +29,7 @@
     <sheet name="02 a 08_09" sheetId="14" r:id="rId14"/>
     <sheet name="09 a 15_09" sheetId="15" r:id="rId15"/>
     <sheet name="16 a 22_09" sheetId="16" r:id="rId16"/>
+    <sheet name="23 a 29_09" sheetId="17" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'07 a 13.07'!$A$4:$B$4</definedName>
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="185">
   <si>
     <t>Código</t>
   </si>
@@ -611,6 +612,9 @@
   </si>
   <si>
     <t>GTVC-145</t>
+  </si>
+  <si>
+    <t>CIBIB</t>
   </si>
 </sst>
 </file>
@@ -5467,6 +5471,596 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3B4A20A-4A75-4BBC-92E8-B902FA34B631}">
+  <dimension ref="A2:C56"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.7265625" customWidth="1"/>
+    <col min="2" max="2" width="16.36328125" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="B2" s="11">
+        <f>C56</f>
+        <v>242</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="8">
+        <v>38</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="8">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="8">
+        <v>30</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" s="8">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="8">
+        <v>29</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C7" s="8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C8" s="8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="8">
+        <v>33</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C9" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="8">
+        <v>5</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C10" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="8">
+        <v>1</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="8">
+        <v>15</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="C12" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="8">
+        <v>32</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="8">
+        <v>43</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="8">
+        <v>28</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C15" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="8">
+        <v>37</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="8">
+        <v>2</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="8">
+        <v>16</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C18" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="8">
+        <v>22</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="C19" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="8">
+        <v>27</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C20" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="8">
+        <v>4</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C21" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="8">
+        <v>36</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="8">
+        <v>8</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="8">
+        <v>31</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C24" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="8">
+        <v>40</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C25" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="8">
+        <v>25</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="8">
+        <v>48</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="8">
+        <v>23</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C28" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="8">
+        <v>42</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="8">
+        <v>13</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="8">
+        <v>41</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" s="8">
+        <v>17</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="C32" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="8">
+        <v>34</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" s="8">
+        <v>26</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C34" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="8">
+        <v>14</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C35" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="8">
+        <v>3</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="C36" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" s="8">
+        <v>0</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C37" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" s="8">
+        <v>9</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C38" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" s="8">
+        <v>10</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" s="8">
+        <v>11</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C40" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" s="8">
+        <v>12</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C41" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" s="8">
+        <v>6</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C42" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" s="8">
+        <v>24</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" s="8">
+        <v>21</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C44" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" s="8">
+        <v>18</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C45" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" s="8">
+        <v>20</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C46" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" s="8">
+        <v>19</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C47" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" s="8">
+        <v>39</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C48" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" s="8">
+        <v>35</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C49" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" s="8">
+        <v>44</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C50" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" s="8">
+        <v>45</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C51" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" s="8">
+        <v>46</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C52" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" s="8">
+        <v>47</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="C53" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" s="8"/>
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C56" s="6">
+        <f>SUM(C5:C55)</f>
+        <v>242</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31DC5A72-105B-4A74-9A40-6DECF5B03B2D}">
   <dimension ref="A2:B61"/>

--- a/ocorrencias.xlsx
+++ b/ocorrencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anac-my.sharepoint.com/personal/luiz_beltrao_anac_gov_br/Documents/7 - CGDIN/SEI/Verificação semanal LGPD/Painel de controle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="67" documentId="8_{B08CBB39-7D29-48D2-BF0D-F3F98B4AE0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8A8932E-DDD4-4018-8945-96876C33AA53}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="8_{B08CBB39-7D29-48D2-BF0D-F3F98B4AE0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B836DC63-BA74-4640-8AEB-41B243E407AB}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="11" activeTab="16" xr2:uid="{A9AF6F09-8019-4632-99BD-44582E7A76AD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="13" activeTab="17" xr2:uid="{A9AF6F09-8019-4632-99BD-44582E7A76AD}"/>
   </bookViews>
   <sheets>
     <sheet name="1 a 8.06" sheetId="2" r:id="rId1"/>
@@ -30,6 +30,7 @@
     <sheet name="09 a 15_09" sheetId="15" r:id="rId15"/>
     <sheet name="16 a 22_09" sheetId="16" r:id="rId16"/>
     <sheet name="23 a 29_09" sheetId="17" r:id="rId17"/>
+    <sheet name="30_09 a 06_10" sheetId="18" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'07 a 13.07'!$A$4:$B$4</definedName>
@@ -60,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="187">
   <si>
     <t>Código</t>
   </si>
@@ -615,6 +616,12 @@
   </si>
   <si>
     <t>CIBIB</t>
+  </si>
+  <si>
+    <t>COAG-MAO</t>
+  </si>
+  <si>
+    <t>CRG-CPPR</t>
   </si>
 </sst>
 </file>
@@ -6061,6 +6068,554 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD4A2E3B-3995-4B66-BC4A-9B5E7F9BDF43}">
+  <dimension ref="A2:C56"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.7265625" customWidth="1"/>
+    <col min="2" max="2" width="16.36328125" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="B2" s="11">
+        <f>C56</f>
+        <v>226</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="8">
+        <v>37</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="8">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="8">
+        <v>28</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" s="8">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="8">
+        <v>29</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7" s="8">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="8">
+        <v>23</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" s="8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="8">
+        <v>1</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="8">
+        <v>31</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="8">
+        <v>27</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C11" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="8">
+        <v>32</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C12" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="8">
+        <v>36</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="8">
+        <v>7</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C14" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="8">
+        <v>33</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="8">
+        <v>16</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="C16" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="8">
+        <v>8</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="8">
+        <v>38</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C18" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="8">
+        <v>4</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C19" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="8">
+        <v>5</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C20" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="8">
+        <v>2</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="8">
+        <v>17</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C22" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="8">
+        <v>35</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="8">
+        <v>18</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="8">
+        <v>3</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="C25" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="8">
+        <v>9</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="8">
+        <v>39</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="8">
+        <v>25</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C28" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="8">
+        <v>19</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="8">
+        <v>11</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="8">
+        <v>41</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C31" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" s="8">
+        <v>30</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C32" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="8">
+        <v>6</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C33" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" s="8">
+        <v>0</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C34" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="8">
+        <v>24</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="8">
+        <v>12</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" s="8">
+        <v>15</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="C37" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" s="8">
+        <v>14</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C38" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" s="8">
+        <v>10</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="C39" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" s="8">
+        <v>22</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="C40" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" s="8">
+        <v>20</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="C41" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" s="8">
+        <v>21</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="C42" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" s="8">
+        <v>13</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C43" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" s="8">
+        <v>26</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C44" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" s="8">
+        <v>34</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C45" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" s="8">
+        <v>40</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C46" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" s="8"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" s="8"/>
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" s="8"/>
+      <c r="B49" s="8"/>
+      <c r="C49" s="8"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" s="8"/>
+      <c r="B50" s="8"/>
+      <c r="C50" s="8"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" s="8"/>
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" s="8"/>
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" s="8"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" s="8"/>
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C56" s="6">
+        <f>SUM(C5:C55)</f>
+        <v>226</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31DC5A72-105B-4A74-9A40-6DECF5B03B2D}">
   <dimension ref="A2:B61"/>
@@ -9823,12 +10378,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="583a6060-d1b7-45db-b4d6-660de356d713">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="97cc50e0-5e48-4896-9dff-357abd4c15c7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10061,20 +10618,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="583a6060-d1b7-45db-b4d6-660de356d713">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="97cc50e0-5e48-4896-9dff-357abd4c15c7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BDE4EE3-4557-4002-B14D-2B12156DBD9E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD91E5EA-D116-4795-B575-F86A672AE76F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="583a6060-d1b7-45db-b4d6-660de356d713"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="97cc50e0-5e48-4896-9dff-357abd4c15c7"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10099,18 +10663,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD91E5EA-D116-4795-B575-F86A672AE76F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BDE4EE3-4557-4002-B14D-2B12156DBD9E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="583a6060-d1b7-45db-b4d6-660de356d713"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="97cc50e0-5e48-4896-9dff-357abd4c15c7"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/ocorrencias.xlsx
+++ b/ocorrencias.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anac-my.sharepoint.com/personal/luiz_beltrao_anac_gov_br/Documents/7 - CGDIN/SEI/Verificação semanal LGPD/Painel de controle/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luiz.beltrao\OneDrive - ANAC\7 - CGDIN\SEI\Verificação semanal LGPD\Painel de controle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="8_{B08CBB39-7D29-48D2-BF0D-F3F98B4AE0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B836DC63-BA74-4640-8AEB-41B243E407AB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F71FF62-78AC-4347-8A18-49502F5EEC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="13" activeTab="17" xr2:uid="{A9AF6F09-8019-4632-99BD-44582E7A76AD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="14" activeTab="18" xr2:uid="{A9AF6F09-8019-4632-99BD-44582E7A76AD}"/>
   </bookViews>
   <sheets>
     <sheet name="1 a 8.06" sheetId="2" r:id="rId1"/>
@@ -31,6 +31,7 @@
     <sheet name="16 a 22_09" sheetId="16" r:id="rId16"/>
     <sheet name="23 a 29_09" sheetId="17" r:id="rId17"/>
     <sheet name="30_09 a 06_10" sheetId="18" r:id="rId18"/>
+    <sheet name="06 a 13_10" sheetId="19" r:id="rId19"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'07 a 13.07'!$A$4:$B$4</definedName>
@@ -61,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="190">
   <si>
     <t>Código</t>
   </si>
@@ -622,6 +623,15 @@
   </si>
   <si>
     <t>CRG-CPPR</t>
+  </si>
+  <si>
+    <t>STD</t>
+  </si>
+  <si>
+    <t>COART</t>
+  </si>
+  <si>
+    <t>GTFC-SIA</t>
   </si>
 </sst>
 </file>
@@ -6616,6 +6626,584 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFF30369-40E7-4ED3-8C2E-F108BE1C0784}">
+  <dimension ref="A2:C56"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.7265625" customWidth="1"/>
+    <col min="2" max="2" width="16.36328125" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="B2" s="11">
+        <f>C56</f>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="8">
+        <v>39</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="8">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="8">
+        <v>28</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" s="8">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="8">
+        <v>29</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7" s="8">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="8">
+        <v>30</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="8">
+        <v>38</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="8">
+        <v>6</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C10" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="8">
+        <v>7</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="C11" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="8">
+        <v>16</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C12" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="8">
+        <v>17</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="C13" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="8">
+        <v>27</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C14" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="8">
+        <v>12</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="8">
+        <v>32</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C16" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="8">
+        <v>13</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="8">
+        <v>44</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="8">
+        <v>8</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C19" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="8">
+        <v>4</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="C20" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="8">
+        <v>3</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="8">
+        <v>46</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="C22" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="8">
+        <v>40</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="8">
+        <v>25</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="8">
+        <v>23</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="8">
+        <v>10</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="8">
+        <v>11</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="8">
+        <v>15</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="C28" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="8">
+        <v>19</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="8">
+        <v>14</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C30" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="8">
+        <v>9</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C31" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" s="8">
+        <v>2</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C32" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="8">
+        <v>1</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C33" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" s="8">
+        <v>0</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C34" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="8">
+        <v>5</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C35" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="8">
+        <v>24</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C36" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" s="8">
+        <v>26</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="C37" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" s="8">
+        <v>21</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" s="8">
+        <v>22</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C39" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" s="8">
+        <v>18</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="C40" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" s="8">
+        <v>20</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C41" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" s="8">
+        <v>33</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="C42" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" s="8">
+        <v>31</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C43" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" s="8">
+        <v>37</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C44" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" s="8">
+        <v>36</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C45" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" s="8">
+        <v>35</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C46" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" s="8">
+        <v>34</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="C47" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" s="8">
+        <v>42</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" s="8">
+        <v>41</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C49" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" s="8">
+        <v>43</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C50" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" s="8">
+        <v>45</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="C51" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" s="8"/>
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" s="8"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" s="8"/>
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C56" s="6">
+        <f>SUM(C5:C55)</f>
+        <v>187</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31DC5A72-105B-4A74-9A40-6DECF5B03B2D}">
   <dimension ref="A2:B61"/>
@@ -10378,17 +10966,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="583a6060-d1b7-45db-b4d6-660de356d713">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="97cc50e0-5e48-4896-9dff-357abd4c15c7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B2C160DC8B30F54783CACC61231B8252" ma:contentTypeVersion="14" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="1f908957678d77794d61d7fffe93fc41">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="583a6060-d1b7-45db-b4d6-660de356d713" xmlns:ns3="97cc50e0-5e48-4896-9dff-357abd4c15c7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0aa59e2dacabcbe879c9d2919b50461b" ns2:_="" ns3:_="">
     <xsd:import namespace="583a6060-d1b7-45db-b4d6-660de356d713"/>
@@ -10617,6 +11194,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="583a6060-d1b7-45db-b4d6-660de356d713">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="97cc50e0-5e48-4896-9dff-357abd4c15c7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -10627,23 +11215,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD91E5EA-D116-4795-B575-F86A672AE76F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="583a6060-d1b7-45db-b4d6-660de356d713"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="97cc50e0-5e48-4896-9dff-357abd4c15c7"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{907A6689-E3B8-4B0E-A078-95B4FF1401C0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10662,6 +11233,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD91E5EA-D116-4795-B575-F86A672AE76F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="583a6060-d1b7-45db-b4d6-660de356d713"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="97cc50e0-5e48-4896-9dff-357abd4c15c7"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BDE4EE3-4557-4002-B14D-2B12156DBD9E}">
   <ds:schemaRefs>

--- a/ocorrencias.xlsx
+++ b/ocorrencias.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luiz.beltrao\OneDrive - ANAC\7 - CGDIN\SEI\Verificação semanal LGPD\Painel de controle\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anac-my.sharepoint.com/personal/luiz_beltrao_anac_gov_br/Documents/7 - CGDIN/SEI/Verificação semanal LGPD/Painel de controle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F71FF62-78AC-4347-8A18-49502F5EEC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{E98B209B-DD9F-433E-9DC3-B87EE7A544D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9097ED27-562F-4385-890E-AB5385A46DEB}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="14" activeTab="18" xr2:uid="{A9AF6F09-8019-4632-99BD-44582E7A76AD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="15" activeTab="19" xr2:uid="{A9AF6F09-8019-4632-99BD-44582E7A76AD}"/>
   </bookViews>
   <sheets>
     <sheet name="1 a 8.06" sheetId="2" r:id="rId1"/>
@@ -31,14 +31,15 @@
     <sheet name="16 a 22_09" sheetId="16" r:id="rId16"/>
     <sheet name="23 a 29_09" sheetId="17" r:id="rId17"/>
     <sheet name="30_09 a 06_10" sheetId="18" r:id="rId18"/>
-    <sheet name="06 a 13_10" sheetId="19" r:id="rId19"/>
+    <sheet name="07 a 13_10" sheetId="19" r:id="rId19"/>
+    <sheet name="14 a 20_10" sheetId="20" r:id="rId20"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'07 a 13.07'!$A$4:$B$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'14 a 20.07'!$A$4:$B$59</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'21 a 27.07'!$A$4:$B$63</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -62,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="191">
   <si>
     <t>Código</t>
   </si>
@@ -632,6 +633,9 @@
   </si>
   <si>
     <t>GTFC-SIA</t>
+  </si>
+  <si>
+    <t>ASAS-TODOS</t>
   </si>
 </sst>
 </file>
@@ -7691,6 +7695,613 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B40820C0-4676-402D-A580-49073B9C2B1B}">
+  <dimension ref="A2:C58"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.7265625" customWidth="1"/>
+    <col min="2" max="2" width="16.36328125" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="B2" s="11">
+        <f>C58</f>
+        <v>243</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="8">
+        <v>42</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="8">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="8">
+        <v>32</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" s="8">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="8">
+        <v>33</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7" s="8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="8">
+        <v>36</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C8" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="8">
+        <v>41</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="8">
+        <v>47</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="8">
+        <v>7</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C11" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="8">
+        <v>31</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C12" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="8">
+        <v>35</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="8">
+        <v>4</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="C14" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="8">
+        <v>17</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C15" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="8">
+        <v>9</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C16" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="8">
+        <v>8</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C17" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="8">
+        <v>21</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="8">
+        <v>27</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="8">
+        <v>46</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="8">
+        <v>13</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="8">
+        <v>1</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="8">
+        <v>3</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="8">
+        <v>28</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="8">
+        <v>12</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="8">
+        <v>16</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="C26" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="8">
+        <v>38</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="8">
+        <v>2</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="8">
+        <v>5</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C29" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="8">
+        <v>18</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C30" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="8">
+        <v>14</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" s="8">
+        <v>10</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="8">
+        <v>45</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" s="8">
+        <v>34</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C34" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="8">
+        <v>25</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C35" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="8">
+        <v>15</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C36" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" s="8">
+        <v>11</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C37" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" s="8">
+        <v>6</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" s="8">
+        <v>0</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="C39" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" s="8">
+        <v>29</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" s="8">
+        <v>30</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="C41" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" s="8">
+        <v>20</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C42" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" s="8">
+        <v>19</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="C43" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" s="8">
+        <v>22</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C44" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" s="8">
+        <v>23</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="C45" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" s="8">
+        <v>24</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="C46" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" s="8">
+        <v>26</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C47" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" s="8">
+        <v>39</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" s="8">
+        <v>40</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C49" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" s="8">
+        <v>37</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C50" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" s="8">
+        <v>44</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" s="8">
+        <v>43</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="C52" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" s="8">
+        <v>48</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="C53" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" s="8">
+        <v>49</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C54" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55" s="8">
+        <v>50</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C55" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C58">
+        <f>SUM(C5:C57)</f>
+        <v>243</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E62610ED-ECEA-4CB8-A4CD-E34BDB82EC00}">
   <dimension ref="A2:B52"/>
@@ -10966,6 +11577,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="583a6060-d1b7-45db-b4d6-660de356d713">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="97cc50e0-5e48-4896-9dff-357abd4c15c7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B2C160DC8B30F54783CACC61231B8252" ma:contentTypeVersion="14" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="1f908957678d77794d61d7fffe93fc41">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="583a6060-d1b7-45db-b4d6-660de356d713" xmlns:ns3="97cc50e0-5e48-4896-9dff-357abd4c15c7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0aa59e2dacabcbe879c9d2919b50461b" ns2:_="" ns3:_="">
     <xsd:import namespace="583a6060-d1b7-45db-b4d6-660de356d713"/>
@@ -11194,17 +11816,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="583a6060-d1b7-45db-b4d6-660de356d713">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="97cc50e0-5e48-4896-9dff-357abd4c15c7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -11215,6 +11826,23 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD91E5EA-D116-4795-B575-F86A672AE76F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="583a6060-d1b7-45db-b4d6-660de356d713"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="97cc50e0-5e48-4896-9dff-357abd4c15c7"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{907A6689-E3B8-4B0E-A078-95B4FF1401C0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11233,23 +11861,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD91E5EA-D116-4795-B575-F86A672AE76F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="583a6060-d1b7-45db-b4d6-660de356d713"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="97cc50e0-5e48-4896-9dff-357abd4c15c7"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BDE4EE3-4557-4002-B14D-2B12156DBD9E}">
   <ds:schemaRefs>

--- a/ocorrencias.xlsx
+++ b/ocorrencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anac-my.sharepoint.com/personal/luiz_beltrao_anac_gov_br/Documents/7 - CGDIN/SEI/Verificação semanal LGPD/Painel de controle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{E98B209B-DD9F-433E-9DC3-B87EE7A544D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9097ED27-562F-4385-890E-AB5385A46DEB}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{E98B209B-DD9F-433E-9DC3-B87EE7A544D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D6C1A7F-2FCD-4F03-8A73-F4E7498050C2}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="15" activeTab="19" xr2:uid="{A9AF6F09-8019-4632-99BD-44582E7A76AD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="16" activeTab="20" xr2:uid="{A9AF6F09-8019-4632-99BD-44582E7A76AD}"/>
   </bookViews>
   <sheets>
     <sheet name="1 a 8.06" sheetId="2" r:id="rId1"/>
@@ -33,6 +33,7 @@
     <sheet name="30_09 a 06_10" sheetId="18" r:id="rId18"/>
     <sheet name="07 a 13_10" sheetId="19" r:id="rId19"/>
     <sheet name="14 a 20_10" sheetId="20" r:id="rId20"/>
+    <sheet name="21  a 27_10" sheetId="21" r:id="rId21"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'07 a 13.07'!$A$4:$B$4</definedName>
@@ -63,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="194">
   <si>
     <t>Código</t>
   </si>
@@ -636,6 +637,15 @@
   </si>
   <si>
     <t>ASAS-TODOS</t>
+  </si>
+  <si>
+    <t>CPEA</t>
+  </si>
+  <si>
+    <t>GTEC</t>
+  </si>
+  <si>
+    <t>PF-ANAC</t>
   </si>
 </sst>
 </file>
@@ -8302,6 +8312,565 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CEAA9C2-15E9-4C30-B2FB-E85AA7A06967}">
+  <dimension ref="A2:C58"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.7265625" customWidth="1"/>
+    <col min="2" max="2" width="16.36328125" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="B2" s="11">
+        <f>C58</f>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="8">
+        <v>24</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C5" s="8">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="8">
+        <v>25</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" s="8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="8">
+        <v>32</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="8">
+        <v>28</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C8" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="8">
+        <v>3</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="8">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="8">
+        <v>37</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="8">
+        <v>7</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C11" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="8">
+        <v>10</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="8">
+        <v>6</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C13" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="8">
+        <v>40</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="8">
+        <v>2</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="8">
+        <v>12</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="8">
+        <v>5</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C17" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="8">
+        <v>23</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C18" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="8">
+        <v>21</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="8">
+        <v>0</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C20" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="8">
+        <v>33</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C21" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="8">
+        <v>4</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C22" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="8">
+        <v>8</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="8">
+        <v>19</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="C24" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="8">
+        <v>11</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="8">
+        <v>35</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="8">
+        <v>31</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="8">
+        <v>16</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C28" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="8">
+        <v>20</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="8">
+        <v>9</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="8">
+        <v>1</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C31" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" s="8">
+        <v>26</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="C32" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="8">
+        <v>22</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C33" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" s="8">
+        <v>17</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="8">
+        <v>13</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C35" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="8">
+        <v>14</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="C36" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" s="8">
+        <v>15</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C37" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" s="8">
+        <v>18</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" s="8">
+        <v>30</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C39" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" s="8">
+        <v>34</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C40" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" s="8">
+        <v>27</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C41" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" s="8">
+        <v>29</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C42" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" s="8">
+        <v>36</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="C43" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" s="8">
+        <v>38</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C44" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" s="8">
+        <v>39</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C45" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" s="8">
+        <v>41</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C46" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" s="8">
+        <v>42</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="C47" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" s="8"/>
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" s="8"/>
+      <c r="B49" s="8"/>
+      <c r="C49" s="8"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" s="8"/>
+      <c r="B50" s="8"/>
+      <c r="C50" s="8"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" s="8"/>
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" s="8"/>
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" s="8"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" s="8"/>
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55" s="8"/>
+      <c r="B55" s="8"/>
+      <c r="C55" s="8"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C58">
+        <f>SUM(C5:C57)</f>
+        <v>174</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E62610ED-ECEA-4CB8-A4CD-E34BDB82EC00}">
   <dimension ref="A2:B52"/>
@@ -11577,17 +12146,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="583a6060-d1b7-45db-b4d6-660de356d713">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="97cc50e0-5e48-4896-9dff-357abd4c15c7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B2C160DC8B30F54783CACC61231B8252" ma:contentTypeVersion="14" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="1f908957678d77794d61d7fffe93fc41">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="583a6060-d1b7-45db-b4d6-660de356d713" xmlns:ns3="97cc50e0-5e48-4896-9dff-357abd4c15c7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0aa59e2dacabcbe879c9d2919b50461b" ns2:_="" ns3:_="">
     <xsd:import namespace="583a6060-d1b7-45db-b4d6-660de356d713"/>
@@ -11816,6 +12374,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="583a6060-d1b7-45db-b4d6-660de356d713">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="97cc50e0-5e48-4896-9dff-357abd4c15c7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -11826,23 +12395,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD91E5EA-D116-4795-B575-F86A672AE76F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="583a6060-d1b7-45db-b4d6-660de356d713"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="97cc50e0-5e48-4896-9dff-357abd4c15c7"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{907A6689-E3B8-4B0E-A078-95B4FF1401C0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11861,6 +12413,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD91E5EA-D116-4795-B575-F86A672AE76F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="583a6060-d1b7-45db-b4d6-660de356d713"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="97cc50e0-5e48-4896-9dff-357abd4c15c7"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BDE4EE3-4557-4002-B14D-2B12156DBD9E}">
   <ds:schemaRefs>
